--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>74.59954749902238</v>
+        <v>12.12242646859114</v>
       </c>
       <c r="D2" t="n">
-        <v>43.82868810789898</v>
+        <v>7.122161817533585</v>
       </c>
       <c r="E2" t="n">
-        <v>24.53369155280659</v>
+        <v>3.986724877331071</v>
       </c>
       <c r="F2" t="n">
-        <v>18.76411450264676</v>
+        <v>3.049168606680098</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.742262719887214</v>
+        <v>0.6081176919816722</v>
       </c>
       <c r="D3" t="n">
-        <v>3.247984098042436</v>
+        <v>0.5277974159318958</v>
       </c>
       <c r="E3" t="n">
-        <v>24.53369155280659</v>
+        <v>3.986724877331071</v>
       </c>
       <c r="F3" t="n">
-        <v>18.76411450264676</v>
+        <v>3.049168606680098</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.42365965879586</v>
+        <v>1.856344694554328</v>
       </c>
       <c r="D4" t="n">
-        <v>12.26730145680538</v>
+        <v>1.993436486730874</v>
       </c>
       <c r="E4" t="n">
-        <v>24.53369155280659</v>
+        <v>3.986724877331071</v>
       </c>
       <c r="F4" t="n">
-        <v>18.76411450264676</v>
+        <v>3.049168606680098</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.15974513746415</v>
+        <v>1.813458584837924</v>
       </c>
       <c r="D5" t="n">
-        <v>37.3955289720739</v>
+        <v>6.07677345796201</v>
       </c>
       <c r="E5" t="n">
-        <v>24.53369155280659</v>
+        <v>3.986724877331071</v>
       </c>
       <c r="F5" t="n">
-        <v>18.76411450264676</v>
+        <v>3.049168606680098</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.83601865002466</v>
+        <v>4.035853030629006</v>
       </c>
       <c r="D6" t="n">
-        <v>25.75436909693153</v>
+        <v>4.185084978251373</v>
       </c>
       <c r="E6" t="n">
-        <v>24.53369155280659</v>
+        <v>3.986724877331071</v>
       </c>
       <c r="F6" t="n">
-        <v>18.76411450264676</v>
+        <v>3.049168606680098</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.15392898128885</v>
+        <v>2.950013459459438</v>
       </c>
       <c r="D7" t="n">
-        <v>25.69939094948296</v>
+        <v>4.176151029290981</v>
       </c>
       <c r="E7" t="n">
-        <v>24.53369155280659</v>
+        <v>3.986724877331071</v>
       </c>
       <c r="F7" t="n">
-        <v>18.76411450264676</v>
+        <v>3.049168606680098</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.50373113550191</v>
+        <v>5.44435630951906</v>
       </c>
       <c r="D8" t="n">
-        <v>34.69829294816947</v>
+        <v>5.63847260407754</v>
       </c>
       <c r="E8" t="n">
-        <v>24.53369155280659</v>
+        <v>3.986724877331071</v>
       </c>
       <c r="F8" t="n">
-        <v>18.76411450264676</v>
+        <v>3.049168606680098</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>1.365367725172715</v>
+        <v>0.2218722553405661</v>
       </c>
       <c r="D9" t="n">
-        <v>33.43005120855513</v>
+        <v>5.432383321390208</v>
       </c>
       <c r="E9" t="n">
-        <v>24.53369155280659</v>
+        <v>3.986724877331071</v>
       </c>
       <c r="F9" t="n">
-        <v>18.76411450264676</v>
+        <v>3.049168606680098</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.96688571430832</v>
+        <v>4.219618928575102</v>
       </c>
       <c r="D10" t="n">
-        <v>46.32394067764724</v>
+        <v>7.527640360117676</v>
       </c>
       <c r="E10" t="n">
-        <v>24.53369155280659</v>
+        <v>3.986724877331071</v>
       </c>
       <c r="F10" t="n">
-        <v>18.76411450264676</v>
+        <v>3.049168606680098</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>48.12743500333256</v>
+        <v>7.820708188041541</v>
       </c>
       <c r="D11" t="n">
-        <v>63.89901080989958</v>
+        <v>10.38358925660868</v>
       </c>
       <c r="E11" t="n">
-        <v>24.53369155280659</v>
+        <v>3.986724877331071</v>
       </c>
       <c r="F11" t="n">
-        <v>18.76411450264676</v>
+        <v>3.049168606680098</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>49.25022770133066</v>
+        <v>8.003162001466233</v>
       </c>
       <c r="D12" t="n">
-        <v>34.81473516503982</v>
+        <v>5.657394464318971</v>
       </c>
       <c r="E12" t="n">
-        <v>24.53369155280659</v>
+        <v>3.986724877331071</v>
       </c>
       <c r="F12" t="n">
-        <v>18.76411450264676</v>
+        <v>3.049168606680098</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>42.57646397363136</v>
+        <v>6.918675395715097</v>
       </c>
       <c r="D13" t="n">
-        <v>47.95106915063873</v>
+        <v>7.792048736978794</v>
       </c>
       <c r="E13" t="n">
-        <v>24.53369155280659</v>
+        <v>3.986724877331071</v>
       </c>
       <c r="F13" t="n">
-        <v>18.76411450264676</v>
+        <v>3.049168606680098</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>58.26113866141697</v>
+        <v>9.467435032480259</v>
       </c>
       <c r="D14" t="n">
-        <v>57.51861964706789</v>
+        <v>9.346775692648533</v>
       </c>
       <c r="E14" t="n">
-        <v>24.53369155280659</v>
+        <v>3.986724877331071</v>
       </c>
       <c r="F14" t="n">
-        <v>18.76411450264676</v>
+        <v>3.049168606680098</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>71.94051838195533</v>
+        <v>11.69033423706774</v>
       </c>
       <c r="D15" t="n">
-        <v>66.49855113673982</v>
+        <v>10.80601455972022</v>
       </c>
       <c r="E15" t="n">
-        <v>24.53369155280659</v>
+        <v>3.986724877331071</v>
       </c>
       <c r="F15" t="n">
-        <v>18.76411450264676</v>
+        <v>3.049168606680098</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>73.12913440098706</v>
+        <v>11.8834843401604</v>
       </c>
       <c r="D16" t="n">
-        <v>70.85835768580577</v>
+        <v>11.51448312394344</v>
       </c>
       <c r="E16" t="n">
-        <v>24.53369155280659</v>
+        <v>3.986724877331071</v>
       </c>
       <c r="F16" t="n">
-        <v>18.76411450264676</v>
+        <v>3.049168606680098</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
